--- a/Excel/Ejercicio_Calibracion_2026-05-04_10-56-04.xlsx
+++ b/Excel/Ejercicio_Calibracion_2026-05-04_10-56-04.xlsx
@@ -2,24 +2,26 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" tabRatio="600" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Repetibilidad" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Repetibilidad 2" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Repetibilidad 3" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Excentricidad" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Excentricidad 2" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Excentricidad 3" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,15 +30,26 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9EAD3"/>
+        <bgColor rgb="FFD9EAD3"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -57,12 +70,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -1931,4 +1945,1114 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Indicacion</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Sentido</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Sección</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Valor (kg)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Der.-Izq.</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="n">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Der.-Izq.</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Centro</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Der.-Izq.</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C5" t="n">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Izq.-Der.</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Centro</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Izq.-Der.</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" t="n">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Promedios por Sección</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Sección</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Promedio (kg)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>1</v>
+      </c>
+      <c r="B11" t="n">
+        <v>330.5</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>3</v>
+      </c>
+      <c r="B12" t="n">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Centro</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>532.5</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Medidores</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Presión</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Modelos</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Humedad</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Modelos</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Temperatura</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Modelos</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Indicacion</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Sentido</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Sección</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Valor (kg)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Der.-Izq.</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="n">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Der.-Izq.</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Centro</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Izq.-Der.</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C5" t="n">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Izq.-Der.</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Centro</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Promedios por Sección</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Sección</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Promedio (kg)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1</v>
+      </c>
+      <c r="B10" t="n">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>3</v>
+      </c>
+      <c r="B11" t="n">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Centro</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Pesas</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Key</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Magnitud</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Identificación</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Modelo</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Serie</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Juego</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Id_pesa</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Nominal</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Unidad</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>masa y masa convencional</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>JGMBE-014</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Sin modelo</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Sin serie</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>masa y masa convencional</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>JGMBE-012</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>IND</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>IND131</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>masa y masa convencional</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>JGMBE-013</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Sin modelo</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Sin serie</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>masa y masa convencional</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>JGMBE-02</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Sin modelo</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Sin serie</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>221</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Medidores</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Magnitud</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Valor Inicial (Ci)</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Hora de Registro</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Presión</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>0.00 Pa</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>15:50:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Humedad</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>0.0 %</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>15:50:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Temperatura</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>0.0 °C</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>15:50:13</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Indicacion</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Sentido</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Sección</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Valor (kg)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Der.-Izq.</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="n">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Der.-Izq.</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Centro</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Izq.-Der.</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C5" t="n">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Izq.-Der.</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Centro</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="7"/>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Promedios por Sección</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Sección</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Promedio (kg)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1</v>
+      </c>
+      <c r="B10" t="n">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>3</v>
+      </c>
+      <c r="B11" t="n">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Centro</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="13"/>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Pesas</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Key</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Magnitud</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Identificación</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Modelo</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Serie</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Juego</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Id_pesa</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Nominal</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Unidad</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>masa y masa convencional</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>LGM-03</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Sin modelo</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Sin serie</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>LGM-03</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>masa y masa convencional</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>JGMBE-012</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>IND</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>IND131</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>masa y masa convencional</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>JGMBE-024</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Sin modelo</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Sin serie</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>786</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+    </row>
+    <row r="19"/>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Medidores</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Magnitud</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Valor Inicial (Ci)</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Valor Final (Cf)</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Hora de Registro</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Presión</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>0.00 Pa</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>15:53:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Humedad</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>0.0 %</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>15:53:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Temperatura</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>0.0 °C</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>15:53:55</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>